--- a/CSharp/SpreadSheetAsDataのテスト/TestData/定義名.xlsx
+++ b/CSharp/SpreadSheetAsDataのテスト/TestData/定義名.xlsx
@@ -11,6 +11,7 @@
     <definedName name="book_range">Sheet2!$C$32:$D$36</definedName>
     <definedName name="cell_name" localSheetId="1">Sheet2!$E$25</definedName>
     <definedName name="range_name" localSheetId="1">Sheet2!$B$23:$C$27</definedName>
+    <definedName name="CustomerName">Sheet2!$F$33</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
@@ -24,6 +25,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetData/>
+  <sheetData>
+    <row r="33">
+      <c r="F33" t="str">
+        <v>山田太郎</v>
+      </c>
+    </row>
+  </sheetData>
 </worksheet>
 </file>